--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Rishi Kant Parajuli</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9846210952</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9846210952</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9846210952</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9846210952</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.69458</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.69458</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +942,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.27214</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.27213999999999</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1015,7 +1005,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1306,7 +1296,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -532,9 +532,9 @@
     <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="28" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,6 +982,418 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:25 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr"/>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -996,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1033,7 +1445,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1054,7 +1466,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -1130,201 +1542,230 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1337679</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Rishi Kant Parajuli</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 20h 53m</t>
         </is>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -494,26 +494,26 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -1397,6 +1397,850 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339279</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9761148007</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>LTP9761148007</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:18:42 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Manakamana Jewellers, dhapakhel, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>jhag3854@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Khadka</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>A02-CDB1</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>14h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338976</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860476919</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9860476919</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:22 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.71485</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Panchamukhi Hanuman Temple, Kharibot, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>deujaabhishek@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>04:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L20-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.35709</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>19h 6m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9818819737</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9808460153</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.70483</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Bank Limited ???????? ?????, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>pt2087077@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.27583</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9818819737</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9808460153</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.70483</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Everest Bank Limited ???????? ?????, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>pt2087077@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.27583</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1408,16 +2252,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1445,7 +2289,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1455,7 +2299,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1466,7 +2310,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -1478,7 +2322,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 26m</t>
         </is>
       </c>
     </row>
@@ -1490,7 +2334,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 53m</t>
+          <t>1d 55m</t>
         </is>
       </c>
     </row>
@@ -1527,7 +2371,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1543,231 +2387,604 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1337679</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Rishi Kant Parajuli</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>1d 20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339279</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:18:42 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>14h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338976</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:22 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>19h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
@@ -1464,10 +1464,8 @@
           <t>Gokul Kumar Jha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9761148007</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9761148007</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1502,10 +1500,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1561,25 +1557,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>A02-CDB1</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1675,10 +1667,8 @@
           <t>Abishek Deuja</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860476919</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860476919</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1713,10 +1703,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.71485</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.71485</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -1772,25 +1760,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L20-7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.35709</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.35709</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -1886,10 +1870,8 @@
           <t>Pradip Tamang</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9818819737</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9818819737</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -1924,10 +1906,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.70483</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.70483</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -1983,25 +1963,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.27583</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.27583</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2097,10 +2073,8 @@
           <t>Pradip Tamang</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9818819737</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9818819737</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2135,10 +2109,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.70483</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.70483</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2194,50 +2166,149 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.27583</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.27583</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>13h 35m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>23h 9m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:01 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : router nt working   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : router nt working   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2332,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2289,7 +2360,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2310,7 +2381,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2824,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2820,7 +2891,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2887,7 +2958,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -2954,7 +3025,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2312,6 +2312,418 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr"/>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Upgrade the Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:26 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2360,7 +2772,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2381,7 +2793,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,56 +483,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="28" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -2724,6 +2724,810 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9867020120</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>chalachitra_fttx</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>kalikasthan dillibzar	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>02:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB258</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339241</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:30:16 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:30:28 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:54:35 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>15h 24m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>16h 24m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851335109</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851335109</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Chowk - Historical landmark P8G3+RR5 Balaju Roundabout Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>keshabb788@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB194</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9851335109</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851335109</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Chowk - Historical landmark P8G3+RR5 Balaju Roundabout Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>keshabb788@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB194</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2735,16 +3539,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2772,7 +3576,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2782,7 +3586,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2793,7 +3597,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -2805,7 +3609,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 26m</t>
+          <t>3h 57m</t>
         </is>
       </c>
     </row>
@@ -2817,7 +3621,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 55m</t>
+          <t>21h 22m</t>
         </is>
       </c>
     </row>
@@ -2854,32 +3658,32 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -2890,148 +3694,138 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="n">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3047,427 +3841,720 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1339279</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Gokul Kumar Jha</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>High Latency</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>14h 21m</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338976</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Abishek Deuja</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>19h 6m</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1338693</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Pradip Tamang</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Blank TV Display</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>13h 35m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1337679</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Rishi Kant Parajuli</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:38:58 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:45:57 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:38:58 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339279</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Gokul Kumar Jha</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:18:42 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:40:06 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>14h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338976</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Abishek Deuja</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 03:33:22 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:39:55 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>19h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1338693</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Pradip Tamang</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>13h 35m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>23h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338693</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Pradip Tamang</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:08:56 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:34:58 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 10:44:21 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>13h 35m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>23h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339133</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Chalachitra Chautari pvt.ltd</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 05:49:47 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:45 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>18h 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -2791,10 +2791,8 @@
           <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9867020120</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9867020120</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -2880,10 +2878,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -2894,7 +2890,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -2980,20 +2976,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3079,10 +3069,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3093,7 +3081,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3189,10 +3177,8 @@
           <t>Keshav Basnet</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851335109</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851335109</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3282,10 +3268,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -3296,7 +3280,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -3392,10 +3376,8 @@
           <t>Keshav Basnet</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9851335109</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9851335109</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3485,10 +3467,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -3499,32 +3479,243 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>2h 15m</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>14h 7m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>not upgraded internet service</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338492</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9849941148</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9849941148</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:25:17 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.77456</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>budhanilkantha near Park Village Resort, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>biki12344@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L54-1</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.36075</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3576,7 +3767,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3586,7 +3777,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3597,7 +3788,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3800,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 57m</t>
+          <t>3h 31m</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3812,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 22m</t>
+          <t>22h 11m</t>
         </is>
       </c>
     </row>
@@ -3680,10 +3871,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -3829,10 +4020,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -4390,7 +4581,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -4457,7 +4648,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -4524,14 +4715,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:35:54 AM</t>
@@ -4555,6 +4746,73 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>14h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338492</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:25:17 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3575,10 +3575,8 @@
           <t>Bikram Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9849941148</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9849941148</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3611,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.77456</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.77456</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -3672,48 +3668,243 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L54-1</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.36075</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.36075</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338308</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9858052904</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:56:27 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Siddhicharan Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>10:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 47m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -3730,13 +3921,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3767,7 +3958,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -3777,7 +3968,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3788,7 +3979,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3991,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 31m</t>
+          <t>3h 10m</t>
         </is>
       </c>
     </row>
@@ -3812,7 +4003,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 11m</t>
+          <t>1d</t>
         </is>
       </c>
     </row>
@@ -3925,10 +4116,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -4124,181 +4315,137 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1339279</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Gokul Kumar Jha</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4318,22 +4465,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4343,29 +4490,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>14h 21m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1338976</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Abishek Deuja</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4385,22 +4532,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4410,39 +4557,39 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>19h 6m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4452,32 +4599,32 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
@@ -4551,32 +4698,32 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4586,64 +4733,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4653,32 +4800,32 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
@@ -4752,67 +4899,201 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>TKT1339348</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Keshav Basnet</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:35:54 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:28 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:00 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>2h 15m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>14h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>TKT1338492</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Bikram Shrestha</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 07:25:17 AM</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>1d 4h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338308</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Ishor Thapa</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 07:56:27 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:18:43 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3778,10 +3778,8 @@
           <t>Ishor Thapa</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9858052904</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9858052904</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -3867,10 +3865,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -3881,30 +3877,233 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>1d 16h 22m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:32 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>one light blinking</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339492</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Mukhiya</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:50:08 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9849090123</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:07:35 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:32:12 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Dhimelwah Kumari Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>grg42589@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -3921,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3930,7 +4129,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3958,7 +4157,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3979,7 +4178,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -4080,14 +4279,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4248,23 +4447,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4276,14 +4475,14 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -4294,19 +4493,19 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -4322,197 +4521,153 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>Specific Website/App is slow</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="n">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1339279</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Gokul Kumar Jha</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4532,22 +4687,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4557,29 +4712,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>14h 21m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1338976</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Abishek Deuja</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4599,22 +4754,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4624,39 +4779,39 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>19h 6m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4666,32 +4821,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4920,32 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4800,64 +4955,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4867,32 +5022,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
@@ -4966,32 +5121,32 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1338492</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bikram Shrestha</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5001,97 +5156,164 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:25:17 AM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>TKT1338492</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Bikram Shrestha</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:25:17 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:12:25 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>TKT1338308</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Ishor Thapa</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Specific Website/App is slow</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 07:56:27 PM</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>1d 16h 22m</t>
         </is>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3973,10 +3973,8 @@
           <t>Shanta Mukhiya</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9849090123</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9849090123</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4048,10 +4046,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH22" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH22" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="inlineStr"/>
       <c r="AJ22" s="3" t="inlineStr"/>
@@ -4066,10 +4062,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4080,7 +4074,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : one light blinking   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4103,6 +4103,209 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339755</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Saubhagya Group</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Saubhagya Group</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9846860411</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>LTP9845908326</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:49:50 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>King's Akabare Jhol MoMo - Momo restaurant M8PP+P5 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>support@saubhagyagroup.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1h 18m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4114,7 +4317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4123,7 +4326,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4151,7 +4354,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4161,7 +4364,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4172,7 +4375,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4387,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 10m</t>
+          <t>2h 52m</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4399,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>21h 56m</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4458,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -4404,10 +4607,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5313,6 +5516,73 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339755</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Saubhagya Group</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:49:50 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:08:01 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1h 18m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -4170,10 +4170,8 @@
           <t>Saubhagya Group</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9846860411</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9846860411</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4263,10 +4261,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4277,30 +4273,444 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1h 18m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1h 18m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:15 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>06:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4317,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4354,7 +4764,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4364,7 +4774,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -4375,7 +4785,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4797,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 52m</t>
+          <t>6h 6m</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4809,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 56m</t>
+          <t>22h 14m</t>
         </is>
       </c>
     </row>
@@ -4458,10 +4868,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -4607,10 +5017,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5549,14 +5959,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:08:01 PM</t>
@@ -5580,6 +5990,140 @@
       <c r="M41" s="5" t="inlineStr">
         <is>
           <t>1h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4369,10 +4369,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4407,10 +4405,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -4462,25 +4458,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -4576,10 +4568,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -4614,10 +4604,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -4669,48 +4657,557 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>red light blinking</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338795</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851020871</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851020871</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:48:01 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.748214</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Gairi Gaun Futsal Park, Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>07:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L9-5</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.32077</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338833</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851136564</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851136564</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>P94C+8GF, Bhaimal Margh Chowk, Kathmandu 44600 near by Easy Mart, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>yatirajbhattarai@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>06:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L31-7</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:23 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4727,7 +5224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4764,7 +5261,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -4774,7 +5271,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4785,7 +5282,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -4797,7 +5294,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 6m</t>
+          <t>5h 17m</t>
         </is>
       </c>
     </row>
@@ -4809,7 +5306,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 14m</t>
+          <t>22h 31m</t>
         </is>
       </c>
     </row>
@@ -4868,10 +5365,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -4886,14 +5383,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -5017,10 +5514,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5040,10 +5537,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -6026,7 +6523,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -6093,14 +6590,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>19 Sep 2026 01:22:55 PM</t>
@@ -6124,6 +6621,140 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>23h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338795</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:48:01 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338833</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4767,10 +4767,8 @@
           <t>Bir chakra Thapa</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851020871</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851020871</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -4805,10 +4803,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.748214</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.748214</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -4860,25 +4856,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L9-5</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.32077</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.32077</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -4974,10 +4966,8 @@
           <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851136564</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851136564</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5067,10 +5057,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5081,7 +5069,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5213,6 +5201,221 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:41 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339545</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Binesh Joshi</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Binesh Joshi</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9840166838</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9843499802</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:46:47 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.68433</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu ,Shankhamul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB668</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.33969</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5224,7 +5427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5261,7 +5464,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5271,7 +5474,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -5282,7 +5485,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5497,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 17m</t>
+          <t>4h 57m</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5509,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 31m</t>
+          <t>21h 21m</t>
         </is>
       </c>
     </row>
@@ -5365,10 +5568,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -5514,10 +5717,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -6657,7 +6860,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -6724,14 +6927,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:17:24 PM</t>
@@ -6755,6 +6958,73 @@
       <c r="M45" s="5" t="inlineStr">
         <is>
           <t>1d 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339545</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Binesh Joshi</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 09:46:47 AM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:41:01 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
@@ -5268,10 +5268,8 @@
           <t>Binesh Joshi</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9840166838</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9840166838</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5306,10 +5304,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.68433</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.68433</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -5347,10 +5343,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -5369,50 +5363,671 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB668</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.33969</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.33969</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>smart tv youtube issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338933</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9851320036</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851320036</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:44:35 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Near By Bode, Madhyapur Thimi 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>05:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L28-5</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>3h 54m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW29" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>set up box collection</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337661</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9849110228</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849110228</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:27:26 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.76959</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Tokha Near By Tokha Ganeshthan Mandir,02, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>bjshresthaa500@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>17:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L27-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.329</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 31m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>new package</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335171</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Som Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Som Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9840062889</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9840062889</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:02:09 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.76023</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Near Sadbhab Banquet, Tokha Rd, Tokha-03, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>somshrestha3669@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>16:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L42-1</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.329</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4d 15h 55m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -5427,7 +6042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5464,7 +6079,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -5474,7 +6089,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5485,7 +6100,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -5497,7 +6112,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 57m</t>
+          <t>4h 10m</t>
         </is>
       </c>
     </row>
@@ -5509,7 +6124,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 21m</t>
+          <t>1d 3h 41m</t>
         </is>
       </c>
     </row>
@@ -5546,79 +6161,79 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -5634,93 +6249,88 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Due to Optical Power flapping</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5731,65 +6341,65 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -5800,35 +6410,35 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -5846,12 +6456,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -5867,305 +6477,173 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>High Latency</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1339279</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Gokul Kumar Jha</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>High Latency</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>14h 21m</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1338976</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Abishek Deuja</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>19h 6m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6175,17 +6653,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -6195,64 +6673,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6262,54 +6740,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6329,22 +6807,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6354,29 +6832,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6396,54 +6874,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6463,54 +6941,54 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1338492</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Bikram Shrestha</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6530,22 +7008,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:25:17 AM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -6555,39 +7033,39 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1338308</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Ishor Thapa</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -6597,64 +7075,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:56:27 PM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 22m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1339755</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Saubhagya Group</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -6664,44 +7142,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:49:50 AM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1h 18m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1338492</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Bikram Shrestha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6716,12 +7194,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6731,64 +7209,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>19 Sep 2026 07:25:17 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1338308</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Ishor Thapa</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -6798,54 +7276,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>18 Sep 2026 07:56:27 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1d 16h 22m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1338795</t>
+          <t>TKT1339755</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Bir chakra Thapa</t>
+          <t>Saubhagya Group</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -6865,22 +7343,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:48:01 PM</t>
+          <t>20 Sep 2026 11:49:50 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -6890,19 +7368,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 34m</t>
+          <t>1h 18m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1338833</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Kopila Poudel Bhattarai</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -6917,12 +7395,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -6932,99 +7410,501 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:15:28 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 1m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>TKT1338846</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:55 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:16:13 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338795</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bir chakra Thapa</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 12:48:01 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:22:40 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338833</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Kopila Poudel Bhattarai</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:15:28 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:17:24 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 1m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>TKT1339545</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Binesh Joshi</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 09:46:47 AM</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>3h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338933</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:44:35 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337661</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:27:26 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335171</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Som Shrestha</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:02:09 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:57:37 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>4d 15h 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5473,10 +5473,8 @@
           <t>Roshan Bhandari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9851320036</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9851320036</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5566,10 +5564,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -5580,7 +5576,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -5666,20 +5662,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Bijay Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9849110228</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9849110228</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -5714,10 +5704,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.76959</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.76959</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -5773,25 +5761,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L27-4</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.329</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.32899999999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -5887,10 +5871,8 @@
           <t>Som Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9840062889</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9840062889</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -5925,10 +5907,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.76023</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.76023</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -5984,50 +5964,675 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L42-1</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.329</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.32899999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>4d 15h 55m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : new package  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:12 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339474</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Mabhendra sahi</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Mabhendra sahi</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9700048213</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9827757657</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:54:39 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>27.66029377081862, 85.35606862323932 GPS Coordinates Nearest: CDB457 (61m Road) Map: CG Imadole, Bag</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB456</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>4d 15h 55m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : new package  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW32" s="3" t="inlineStr">
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>5g name not showing</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338698</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Yadav</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Yadav</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9817780679</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9817780679</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:38:14 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68416</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>27.67567408847685, 85.32718108233304 GPS Coordinates Nearest: CDB643 (16m Road) Map: CG Kupandole, B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>by856338@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>08:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB233</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.32352</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339313</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9843807398</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9843807398</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:55:19 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.67113</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>27.67113, 85.3247, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>tamrakarrahisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.3247</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6079,7 +6684,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -6089,7 +6694,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6100,7 +6705,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6717,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 10m</t>
+          <t>3h 36m</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6729,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 41m</t>
+          <t>1d 2h 8m</t>
         </is>
       </c>
     </row>
@@ -6201,10 +6806,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -6251,155 +6856,150 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Device Recovery</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Setup Box Recovery</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -6415,41 +7015,41 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6461,14 +7061,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -6479,19 +7079,19 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -6502,12 +7102,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -6530,264 +7130,176 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
+          <t>High Latency</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
-      <c r="C30" s="3" t="n">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1339279</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Gokul Kumar Jha</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>High Latency</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1338976</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Abishek Deuja</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6807,22 +7319,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6832,39 +7344,39 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>19h 6m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -6874,64 +7386,64 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -6941,64 +7453,64 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7008,54 +7520,54 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7075,64 +7587,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7142,64 +7654,64 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1338492</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bikram Shrestha</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -7209,64 +7721,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:25:17 AM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1338308</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Ishor Thapa</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -7276,44 +7788,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:56:27 PM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 16h 22m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1339755</t>
+          <t>TKT1338492</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Saubhagya Group</t>
+          <t>Bikram Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7343,22 +7855,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:49:50 AM</t>
+          <t>19 Sep 2026 07:25:17 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -7368,39 +7880,39 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1h 18m</t>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1338308</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Ishor Thapa</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -7410,44 +7922,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>18 Sep 2026 07:56:27 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1d 16h 22m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1339755</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Saubhagya Group</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7462,12 +7974,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7477,64 +7989,64 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 11:49:50 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1h 18m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1338795</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Bir chakra Thapa</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -7544,44 +8056,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:48:01 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 34m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1338833</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Kopila Poudel Bhattarai</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7596,12 +8108,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -7611,54 +8123,54 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:15:28 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 1m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1339545</t>
+          <t>TKT1338795</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Binesh Joshi</t>
+          <t>Bir chakra Thapa</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -7678,22 +8190,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:46:47 AM</t>
+          <t>19 Sep 2026 12:48:01 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -7703,29 +8215,29 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>3h 54m</t>
+          <t>1d 34m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1338933</t>
+          <t>TKT1338833</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Roshan Bhandari</t>
+          <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -7740,27 +8252,27 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:44:35 PM</t>
+          <t>19 Sep 2026 01:15:28 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -7770,29 +8282,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>23h 5m</t>
+          <t>1d 1m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1337661</t>
+          <t>TKT1339545</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Bijay Shrestha</t>
+          <t>Binesh Joshi</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -7807,27 +8319,27 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 12:27:26 PM</t>
+          <t>20 Sep 2026 09:46:47 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -7837,74 +8349,409 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 31m</t>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>TKT1338933</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Bhandari</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:44:35 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:50:06 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>23h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337661</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Bijay Shrestha</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:27:26 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:58:39 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>TKT1335171</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Som Shrestha</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Device Recovery</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Setup Box Recovery</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Case : new package  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Case : new package  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:02:09 PM</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>4d 15h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339474</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Mabhendra sahi</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:54:39 AM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:12:42 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338698</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Birendra Yadav</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 11:38:14 AM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:07:20 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339313</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:55:19 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW35"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6074,10 +6074,8 @@
           <t>Mabhendra sahi</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9700048213</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9700048213</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6163,10 +6161,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -6177,7 +6173,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6273,10 +6269,8 @@
           <t>Birendra Yadav</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9817780679</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9817780679</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6311,10 +6305,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68416</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68416</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6352,10 +6344,8 @@
           <t>Configuration Issue</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
@@ -6374,25 +6364,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB233</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.32352</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.32352</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6488,10 +6474,8 @@
           <t>Rahisha Tamrakar</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9843807398</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9843807398</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6526,10 +6510,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.67113</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.67113</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -6567,10 +6549,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -6589,48 +6569,466 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>4,7</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.3247</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.32470000000001</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>17h 10m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.670011</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Daju bhai mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>9861435546@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB265</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.249608</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.670011</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Daju bhai mart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9861435546@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>10:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB265</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.249608</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6647,7 +7045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6684,7 +7082,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -6694,7 +7092,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6705,7 +7103,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6717,7 +7115,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 36m</t>
+          <t>5h 43m</t>
         </is>
       </c>
     </row>
@@ -6729,7 +7127,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 8m</t>
+          <t>1d 2h 22m</t>
         </is>
       </c>
     </row>
@@ -6806,10 +7204,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -6996,10 +7394,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -8587,7 +8985,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -8654,7 +9052,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -8721,14 +9119,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 02:06:16 PM</t>
@@ -8752,6 +9150,140 @@
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>17h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6679,10 +6679,8 @@
           <t>Sunil Basnet</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9861435546</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9861435546</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -6717,10 +6715,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.670011</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.670011</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -6776,25 +6772,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>CDB265</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.249608</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.24960799999999</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -6890,10 +6882,8 @@
           <t>Sunil Basnet</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9861435546</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9861435546</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -6928,10 +6918,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.670011</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.670011</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -6987,48 +6975,147 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB265</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.249608</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.24960799999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 52m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 52m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:35 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr"/>
+      <c r="AA38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7054,7 +7141,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7082,7 +7169,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -7103,7 +7190,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9273,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -9253,7 +9340,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW38"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7121,6 +7121,1021 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338844</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana Baral</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9842684993</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 02:38:58 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>BKT9842684993</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 01:22:07 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:02:01 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Futsal - Futsal court MC96+P25 Araniko Highway Suryabinayak 44800, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>9842684993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 23m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV remote issue</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339979</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9744235441</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9744235441</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:34:26 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Police Station, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L32-8</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1h 19m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:59 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340084</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9841582320</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:41:35 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.675955</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ward no:10,Boshigau,near Basic Learning English Secondary School, Bagmati, Central, Nep</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.247036</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:57 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Skycom to net TV</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1338449</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Sadik Aakhtar Ansari</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9813761666</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:38:45 AM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9851244184</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:34:55 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:57:12 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.732722</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Ganga Hall Marg Kathmandu 44600 near by Kohinoor School - University, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>ss93official@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.304031</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 18m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 8h 22m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337927</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9745867186</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:21 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders, MAKUTE PROFESSIONAL POWER TOOLS - Hardware store ?? ??????? ?????, Kathmandu 44600,</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>agchirag0811@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>14:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 23m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7132,7 +8147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7141,7 +8156,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7169,7 +8184,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -7179,7 +8194,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -7190,7 +8205,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -7202,7 +8217,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 43m</t>
+          <t>5h 4m</t>
         </is>
       </c>
     </row>
@@ -7214,7 +8229,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 22m</t>
+          <t>1d 1h 15m</t>
         </is>
       </c>
     </row>
@@ -7291,10 +8306,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -7309,14 +8324,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -7363,14 +8378,14 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -7481,10 +8496,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -7500,14 +8515,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -7523,7 +8538,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -7541,19 +8556,19 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7564,42 +8579,42 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -7610,19 +8625,19 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -7633,12 +8648,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -7661,14 +8676,14 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -7677,248 +8692,160 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>TKT1339279</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Gokul Kumar Jha</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>High Latency</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>14h 21m</t>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1338976</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Abishek Deuja</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -7938,22 +8865,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7963,39 +8890,39 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>19h 6m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -8005,64 +8932,64 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -8072,64 +8999,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -8139,54 +9066,54 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8206,64 +9133,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -8273,64 +9200,64 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1338492</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Bikram Shrestha</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8340,64 +9267,64 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:25:17 AM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1338308</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Ishor Thapa</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -8407,44 +9334,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:56:27 PM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 16h 22m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1339755</t>
+          <t>TKT1338492</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Saubhagya Group</t>
+          <t>Bikram Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8474,22 +9401,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:49:50 AM</t>
+          <t>19 Sep 2026 07:25:17 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8499,39 +9426,39 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1h 18m</t>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1338308</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Ishor Thapa</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -8541,44 +9468,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>18 Sep 2026 07:56:27 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1d 16h 22m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1339755</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Saubhagya Group</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -8593,12 +9520,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -8608,64 +9535,64 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 11:49:50 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1h 18m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1338795</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Bir chakra Thapa</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -8675,44 +9602,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:48:01 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 34m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1338833</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Kopila Poudel Bhattarai</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8727,12 +9654,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -8742,54 +9669,54 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:15:28 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 1m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1339545</t>
+          <t>TKT1338795</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Binesh Joshi</t>
+          <t>Bir chakra Thapa</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -8809,22 +9736,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:46:47 AM</t>
+          <t>19 Sep 2026 12:48:01 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -8834,29 +9761,29 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>3h 54m</t>
+          <t>1d 34m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1338933</t>
+          <t>TKT1338833</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Roshan Bhandari</t>
+          <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8876,22 +9803,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:44:35 PM</t>
+          <t>19 Sep 2026 01:15:28 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -8901,29 +9828,29 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>23h 5m</t>
+          <t>1d 1m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1337661</t>
+          <t>TKT1339545</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Bijay Shrestha</t>
+          <t>Binesh Joshi</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -8943,22 +9870,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 12:27:26 PM</t>
+          <t>20 Sep 2026 09:46:47 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -8968,29 +9895,29 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 31m</t>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1335171</t>
+          <t>TKT1338933</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Som Shrestha</t>
+          <t>Roshan Bhandari</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -9010,22 +9937,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : new package  has been updated by Sanjeev Giri</t>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:37 PM</t>
+          <t>20 Sep 2026 01:50:06 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:02:09 PM</t>
+          <t>19 Sep 2026 02:44:35 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:37 PM</t>
+          <t>20 Sep 2026 01:50:06 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -9035,29 +9962,29 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>4d 15h 55m</t>
+          <t>23h 5m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1339474</t>
+          <t>TKT1337661</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Mabhendra sahi</t>
+          <t>Bijay Shrestha</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -9077,22 +10004,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:12:42 PM</t>
+          <t>20 Sep 2026 01:58:39 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:54:39 AM</t>
+          <t>18 Sep 2026 12:27:26 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:12:42 PM</t>
+          <t>20 Sep 2026 01:58:39 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -9102,29 +10029,29 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>5h 18m</t>
+          <t>2d 1h 31m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1338698</t>
+          <t>TKT1335171</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Birendra Yadav</t>
+          <t>Som Shrestha</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -9144,22 +10071,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:20 PM</t>
+          <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:38:14 AM</t>
+          <t>15 Sep 2026 10:02:09 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:20 PM</t>
+          <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -9169,19 +10096,19 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 29m</t>
+          <t>4d 15h 55m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1339313</t>
+          <t>TKT1339474</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Rahisha Tamrakar</t>
+          <t>Mabhendra sahi</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -9211,22 +10138,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:06:16 PM</t>
+          <t>20 Sep 2026 02:12:42 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:55:19 PM</t>
+          <t>20 Sep 2026 08:54:39 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:06:16 PM</t>
+          <t>20 Sep 2026 02:12:42 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -9236,39 +10163,39 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>17h 10m</t>
+          <t>5h 18m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1338564</t>
+          <t>TKT1338698</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Sunil Basnet</t>
+          <t>Birendra Yadav</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -9278,99 +10205,434 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>20 Sep 2026 02:07:20 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>19 Sep 2026 11:38:14 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:18:15 PM</t>
+          <t>20 Sep 2026 02:07:20 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>1d 2h 29m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
+          <t>TKT1339313</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Rahisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 08:55:19 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>17h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>TKT1338564</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Sunil Basnet</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 02:18:15 PM</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>1d 4h 52m</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>1d 4h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1338564</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Sunil Basnet</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:25:57 AM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:18:15 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339979</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:34:26 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>1h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340084</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:41:35 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337927</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Traders</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:21 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:55:53 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 23m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="30" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -7188,10 +7188,8 @@
           <t>Kalpana Baral</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9842684993</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9842684993</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7277,10 +7275,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7291,7 +7287,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7387,10 +7383,8 @@
           <t>Sujan Bhujel</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9744235441</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9744235441</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7476,10 +7470,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -7490,7 +7482,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -7586,10 +7578,8 @@
           <t>Raju Maharjan</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9841582320</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9841582320</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -7624,10 +7614,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.675955</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.675955</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -7679,25 +7667,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.247036</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.24703599999999</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -7783,20 +7767,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Sadik Aakhtar Ansari</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9813761666</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9813761666</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -7831,10 +7809,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.732722</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.732722</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -7886,25 +7862,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.304031</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.30403099999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Skycom to net TV  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8000,10 +7972,8 @@
           <t>Madhav Traders</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9745867186</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9745867186</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8093,10 +8063,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -8107,30 +8075,663 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 23m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339147</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Keshab pariyar</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Keshab pariyar</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9763494932</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>BKT9763494932</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:06:53 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-CG Group</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>bhaktapur , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>01:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 23m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>21h 14m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:31 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Net TV Issue</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339263</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:50:17 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.70515</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>P842+3W9, ???????: ?????, Kathmandu 44600 near Paropakar Furniture, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>sabinmagar4152@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>00:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.302205</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>19h 41m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:22 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336061</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Shakti Kumar Godar</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Shakti Kumar Godar</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9855053649</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9855053649</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:29:28 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.743596</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Tokha ward no:11,near Nirmal Batika Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>godarshaktikumar7@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.31971</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 53m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8147,13 +8748,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -8184,7 +8785,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -8194,7 +8795,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -8205,7 +8806,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8818,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 4m</t>
+          <t>4h 34m</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8830,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 15m</t>
+          <t>1d 3h 11m</t>
         </is>
       </c>
     </row>
@@ -8306,10 +8907,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -8342,10 +8943,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -8510,12 +9111,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -8538,18 +9139,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8561,18 +9162,18 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8584,41 +9185,41 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -8630,14 +9231,14 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -8648,12 +9249,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -8671,19 +9272,19 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -8694,12 +9295,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -8722,264 +9323,176 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>TKT1337679</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Rishi Kant Parajuli</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>18 Sep 2026 12:45:57 PM</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 09:38:58 AM</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>TKT1339279</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Gokul Kumar Jha</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Slow Internet Connection</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>High Latency</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>19 Sep 2026 08:18:42 PM</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>20 Sep 2026 10:40:06 AM</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>14h 21m</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1338976</t>
+          <t>TKT1337679</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Abishek Deuja</t>
+          <t>Rishi Kant Parajuli</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -8999,22 +9512,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 03:33:22 PM</t>
+          <t>18 Sep 2026 12:45:57 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:39:55 AM</t>
+          <t>20 Sep 2026 09:38:58 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -9024,39 +9537,39 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>19h 6m</t>
+          <t>1d 20h 53m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1339279</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Gokul Kumar Jha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9066,64 +9579,64 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 08:18:42 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:40:06 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>14h 21m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1338693</t>
+          <t>TKT1338976</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Pradip Tamang</t>
+          <t>Abishek Deuja</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -9133,64 +9646,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:08:56 PM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:34:58 AM</t>
+          <t>19 Sep 2026 03:33:22 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 10:44:21 AM</t>
+          <t>20 Sep 2026 10:39:55 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>13h 35m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>23h 9m</t>
+          <t>19h 6m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1339133</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Chalachitra Chautari pvt.ltd</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>High Latency</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9200,54 +9713,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 05:49:47 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:45 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>18h 1m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1338693</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Pradip Tamang</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -9267,64 +9780,64 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>19 Sep 2026 09:08:56 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 11:34:58 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 10:44:21 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>13h 35m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>23h 9m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1339348</t>
+          <t>TKT1339133</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Keshav Basnet</t>
+          <t>Chalachitra Chautari pvt.ltd</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>High Latency</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9334,64 +9847,64 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:35:54 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:43:28 PM</t>
+          <t>19 Sep 2026 05:49:47 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:51:00 AM</t>
+          <t>20 Sep 2026 11:51:45 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>14h 7m</t>
+          <t>18h 1m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1338492</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Bikram Shrestha</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -9401,64 +9914,64 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 07:25:17 AM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:12:25 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 47m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1338308</t>
+          <t>TKT1339348</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Ishor Thapa</t>
+          <t>Keshav Basnet</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -9468,44 +9981,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : iptv issue     has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 09:35:54 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 07:56:27 PM</t>
+          <t>19 Sep 2026 09:43:28 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 12:18:43 PM</t>
+          <t>20 Sep 2026 11:51:00 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 15m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 16h 22m</t>
+          <t>14h 7m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1339755</t>
+          <t>TKT1338492</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Saubhagya Group</t>
+          <t>Bikram Shrestha</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9535,22 +10048,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : not upgraded internet service  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 11:49:50 AM</t>
+          <t>19 Sep 2026 07:25:17 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:08:01 PM</t>
+          <t>20 Sep 2026 12:12:25 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9560,39 +10073,39 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1h 18m</t>
+          <t>1d 4h 47m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1338308</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Ishor Thapa</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -9602,44 +10115,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : slow internet issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>18 Sep 2026 07:56:27 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 12:18:43 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1d 16h 22m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1338846</t>
+          <t>TKT1339755</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Saubhagya Group</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -9654,12 +10167,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9669,64 +10182,64 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:22:55 PM</t>
+          <t>20 Sep 2026 11:49:50 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:16:13 PM</t>
+          <t>20 Sep 2026 01:08:01 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>23h 53m</t>
+          <t>1h 18m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1338795</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Bir chakra Thapa</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9736,44 +10249,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 12:48:01 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:22:40 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 34m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1338833</t>
+          <t>TKT1338846</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Kopila Poudel Bhattarai</t>
+          <t>Raju Maharjan</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -9788,12 +10301,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -9803,54 +10316,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 01:15:28 PM</t>
+          <t>19 Sep 2026 01:22:55 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:17:24 PM</t>
+          <t>20 Sep 2026 01:16:13 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 53m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1d 1m</t>
+          <t>23h 53m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1339545</t>
+          <t>TKT1338795</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Binesh Joshi</t>
+          <t>Bir chakra Thapa</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -9870,22 +10383,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>Case : red light blinking   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 09:46:47 AM</t>
+          <t>19 Sep 2026 12:48:01 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:41:01 PM</t>
+          <t>20 Sep 2026 01:22:40 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -9895,29 +10408,29 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>3h 54m</t>
+          <t>1d 34m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1338933</t>
+          <t>TKT1338833</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Roshan Bhandari</t>
+          <t>Kopila Poudel Bhattarai</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -9937,22 +10450,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 02:44:35 PM</t>
+          <t>19 Sep 2026 01:15:28 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:50:06 PM</t>
+          <t>20 Sep 2026 01:17:24 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -9962,29 +10475,29 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>23h 5m</t>
+          <t>1d 1m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1337661</t>
+          <t>TKT1339545</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Bijay Shrestha</t>
+          <t>Binesh Joshi</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -10004,22 +10517,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>18 Sep 2026 12:27:26 PM</t>
+          <t>20 Sep 2026 09:46:47 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:58:39 PM</t>
+          <t>20 Sep 2026 01:41:01 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -10029,29 +10542,29 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 31m</t>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1335171</t>
+          <t>TKT1338933</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Som Shrestha</t>
+          <t>Roshan Bhandari</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Device Recovery</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -10071,22 +10584,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : new package  has been updated by Sanjeev Giri</t>
+          <t>Case : smart tv youtube issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:37 PM</t>
+          <t>20 Sep 2026 01:50:06 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:02:09 PM</t>
+          <t>19 Sep 2026 02:44:35 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:57:37 PM</t>
+          <t>20 Sep 2026 01:50:06 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -10096,29 +10609,29 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>4d 15h 55m</t>
+          <t>23h 5m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1339474</t>
+          <t>TKT1337661</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Mabhendra sahi</t>
+          <t>Bijay Shrestha</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -10138,22 +10651,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : set up box collection   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:12:42 PM</t>
+          <t>20 Sep 2026 01:58:39 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:54:39 AM</t>
+          <t>18 Sep 2026 12:27:26 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:12:42 PM</t>
+          <t>20 Sep 2026 01:58:39 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -10163,29 +10676,29 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>5h 18m</t>
+          <t>2d 1h 31m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1338698</t>
+          <t>TKT1335171</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Birendra Yadav</t>
+          <t>Som Shrestha</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>Device Recovery</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Setup Box Recovery</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -10205,22 +10718,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+          <t>Case : new package  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:20 PM</t>
+          <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 11:38:14 AM</t>
+          <t>15 Sep 2026 10:02:09 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:07:20 PM</t>
+          <t>20 Sep 2026 01:57:37 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -10230,19 +10743,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 29m</t>
+          <t>4d 15h 55m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1339313</t>
+          <t>TKT1339474</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Rahisha Tamrakar</t>
+          <t>Mabhendra sahi</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -10272,22 +10785,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:06:16 PM</t>
+          <t>20 Sep 2026 02:12:42 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 08:55:19 PM</t>
+          <t>20 Sep 2026 08:54:39 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:06:16 PM</t>
+          <t>20 Sep 2026 02:12:42 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -10297,39 +10810,39 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>17h 10m</t>
+          <t>5h 18m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1338564</t>
+          <t>TKT1338698</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Sunil Basnet</t>
+          <t>Birendra Yadav</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -10339,44 +10852,44 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>20 Sep 2026 02:07:20 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>19 Sep 2026 11:38:14 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:18:15 PM</t>
+          <t>20 Sep 2026 02:07:20 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>1d 2h 29m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1338564</t>
+          <t>TKT1339313</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Sunil Basnet</t>
+          <t>Rahisha Tamrakar</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -10391,12 +10904,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -10406,111 +10919,111 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>20 Sep 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>19 Sep 2026 09:25:57 AM</t>
+          <t>19 Sep 2026 08:55:19 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:18:15 PM</t>
+          <t>20 Sep 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 52m</t>
+          <t>17h 10m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1339979</t>
+          <t>TKT1338564</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Sujan Bhujel</t>
+          <t>Sunil Basnet</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:54:21 PM</t>
+          <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 01:34:26 PM</t>
+          <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:54:21 PM</t>
+          <t>20 Sep 2026 02:18:15 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 4h 52m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1h 19m</t>
+          <t>1d 4h 52m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1340084</t>
+          <t>TKT1338564</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Raju Maharjan</t>
+          <t>Sunil Basnet</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -10525,114 +11038,449 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:59:20 PM</t>
+          <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:41:35 PM</t>
+          <t>19 Sep 2026 09:25:57 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 02:59:20 PM</t>
+          <t>20 Sep 2026 02:18:15 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 4h 52m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>17m</t>
+          <t>1d 4h 52m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>TKT1339979</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bhujel</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV remote issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 01:34:26 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:54:21 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340084</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Raju Maharjan</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:41:35 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:59:20 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>TKT1337927</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Madhav Traders</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 02:55:53 PM</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026 03:32:21 PM</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 02:55:53 PM</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>1d 23h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339147</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Keshab pariyar</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 06:06:53 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:21:02 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>21h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339263</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 07:50:17 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:31:28 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>19h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1336061</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Shakti Kumar Godar</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 06:29:28 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:22:28 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>3d 20h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8167,10 +8167,8 @@
           <t>Keshab pariyar</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9763494932</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9763494932</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8205,10 +8203,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8268,25 +8264,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8382,10 +8374,8 @@
           <t>Sabin Magar</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9813664152</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9813664152</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8420,10 +8410,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.70515</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.70515</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -8479,25 +8467,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.302205</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.302205</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -8593,10 +8577,8 @@
           <t>Shakti Kumar Godar</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9855053649</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9855053649</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -8631,10 +8613,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.743596</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.743596</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -8690,50 +8670,464 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>2,14</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.31971</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.31971</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3d 20h 53m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:42 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339778</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Manandhar</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Manandhar</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9823489535</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9823489535</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:04:35 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.6782</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Near 6/9 Khaja Ghar, Madhyapur Thimi, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>kishanmanandhar26@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L63-3</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.38727</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>3d 20h 53m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3h 38m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Net TV</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339347</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Bikram Gajurel</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:36:57 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9803749646</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>19 Sep 2026 09:43:03 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:36:57 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.70089</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>kwahiti marga near suzuki showroom and near siddhi ganesh motorcycle workshop teku, Bagmati, Central</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>vgajurel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.30298</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -8748,7 +9142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8785,7 +9179,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -8795,7 +9189,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -8806,7 +9200,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -8818,7 +9212,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 34m</t>
+          <t>4h 25m</t>
         </is>
       </c>
     </row>
@@ -8830,7 +9224,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 11m</t>
+          <t>1d 2h 25m</t>
         </is>
       </c>
     </row>
@@ -8907,10 +9301,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -8925,14 +9319,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -9097,10 +9491,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -9189,14 +9583,14 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11710,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -11383,7 +11777,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : Net TV Issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -11450,14 +11844,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 03:22:28 PM</t>
@@ -11481,6 +11875,73 @@
       <c r="M69" s="5" t="inlineStr">
         <is>
           <t>3d 20h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339778</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Manandhar</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:04:35 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:42:51 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3h 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -8780,10 +8780,8 @@
           <t>Kishan Manandhar</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9823489535</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9823489535</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -8818,10 +8816,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.6782</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.6782</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -8877,25 +8873,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>L63-3</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.38727</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.38727</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -8991,10 +8983,8 @@
           <t>Bikram Gajurel</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9803749646</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9803749646</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9029,10 +9019,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.70089</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.70089</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9084,50 +9072,249 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.30298</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.30298000000001</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337833</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841482102</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841482102S</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:28 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Ratna Rajya Sec. School, M8WP+7XM, Devkota Sadak, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>sumitrashrestha1444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>15:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>L52-6</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>17h 53m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Net TV  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9179,7 +9366,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9189,7 +9376,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -9200,7 +9387,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9399,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 25m</t>
+          <t>4h 17m</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9411,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 25m</t>
+          <t>1d 3h 8m</t>
         </is>
       </c>
     </row>
@@ -9301,10 +9488,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -9491,10 +9678,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -11911,14 +12098,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 03:42:51 PM</t>
@@ -11942,6 +12129,73 @@
       <c r="M70" s="3" t="inlineStr">
         <is>
           <t>3h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1337833</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Sumitra Shrestha</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:50:28 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 03:58:35 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9182,10 +9182,8 @@
           <t>Sumitra Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841482102</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841482102</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9275,10 +9273,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -9289,30 +9285,133 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>2d 1h 8m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 3:59 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr"/>
+      <c r="AM50" s="3" t="inlineStr"/>
+      <c r="AN50" s="3" t="inlineStr"/>
+      <c r="AO50" s="3" t="inlineStr"/>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9338,7 +9437,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9366,7 +9465,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9387,7 +9486,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12264,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9417,6 +9417,209 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339911</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>tej krishna shrestha</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>tej krishna shrestha</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9860466835</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>CHB9860466835</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:18 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Chapabot, Gothatar Chapabot, Gothatar - Historical landmark P95M+269 Kageshwori Manohara 44600, Kath</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9841659170@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9428,7 +9631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9437,7 +9640,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9465,7 +9668,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9475,7 +9678,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -9486,7 +9689,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9701,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 17m</t>
+          <t>4h 9m</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9713,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 8m</t>
+          <t>1d 2h 25m</t>
         </is>
       </c>
     </row>
@@ -9587,10 +9790,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -9777,10 +9980,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -12298,6 +12501,73 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339911</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>tej krishna shrestha</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:58:18 PM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:05 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -9484,10 +9484,8 @@
           <t>tej krishna shrestha</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9860466835</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9860466835</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -9577,10 +9575,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -9591,32 +9587,235 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 25m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339837</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Tripathiand brothers Automobile pvt ltd</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Tripathiand brothers Automobile pvt ltd</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851351926</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851351926</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:25:46 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>27.684280386708334, 85.30324177112256, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>9851351926@GIMAL.COM</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>3h 25m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -9631,11 +9830,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -9668,7 +9867,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -9678,7 +9877,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9689,7 +9888,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9900,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 9m</t>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9912,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 25m</t>
+          <t>1d 1h 46m</t>
         </is>
       </c>
     </row>
@@ -9790,10 +9989,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -9980,10 +10179,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -12534,14 +12733,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 04:24:05 PM</t>
@@ -12565,6 +12764,73 @@
       <c r="M72" s="3" t="inlineStr">
         <is>
           <t>3h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1339837</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Tripathiand brothers Automobile pvt ltd</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 12:25:46 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:33:19 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9683,10 +9683,8 @@
           <t>Tripathiand brothers Automobile pvt ltd</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851351926</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851351926</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -9776,10 +9774,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
@@ -9790,32 +9786,449 @@
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339757</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Padam Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Padam Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9843233935</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9843233935</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:40 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.707875</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>27.707875, 85.323431, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.323431</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>4h 7m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>4h 32m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW52" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:52 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr"/>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" s="3" t="inlineStr"/>
+      <c r="W54" s="3" t="inlineStr"/>
+      <c r="X54" s="3" t="inlineStr"/>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr"/>
+      <c r="AA54" s="3" t="inlineStr"/>
+      <c r="AB54" s="3" t="inlineStr"/>
+      <c r="AC54" s="3" t="inlineStr"/>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr"/>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr"/>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr"/>
+      <c r="AM54" s="3" t="inlineStr"/>
+      <c r="AN54" s="3" t="inlineStr"/>
+      <c r="AO54" s="3" t="inlineStr"/>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 4:32 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr"/>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr"/>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
+      <c r="W55" s="3" t="inlineStr"/>
+      <c r="X55" s="3" t="inlineStr"/>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr"/>
+      <c r="AA55" s="3" t="inlineStr"/>
+      <c r="AB55" s="3" t="inlineStr"/>
+      <c r="AC55" s="3" t="inlineStr"/>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr"/>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr"/>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr"/>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr"/>
+      <c r="AM55" s="3" t="inlineStr"/>
+      <c r="AN55" s="3" t="inlineStr"/>
+      <c r="AO55" s="3" t="inlineStr"/>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9830,7 +10243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9867,7 +10280,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -9877,7 +10290,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -9888,7 +10301,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10313,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 2m</t>
+          <t>3h 55m</t>
         </is>
       </c>
     </row>
@@ -9912,7 +10325,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 46m</t>
+          <t>1d 1h 9m</t>
         </is>
       </c>
     </row>
@@ -9989,10 +10402,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -10179,10 +10592,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -12800,14 +13213,14 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 04:33:19 PM</t>
@@ -12831,6 +13244,73 @@
       <c r="M73" s="5" t="inlineStr">
         <is>
           <t>4h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1339757</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Padam Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 11:51:40 AM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 04:24:28 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>4h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW55"/>
+  <dimension ref="A1:AW56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9882,10 +9882,8 @@
           <t>Padam Bahadur Karki</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9843233935</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9843233935</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -9920,10 +9918,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.707875</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.707875</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -9979,25 +9975,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.323431</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.323431</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10232,6 +10224,213 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340092</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh rai</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh rai</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9818733606</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9818733606</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.696071</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>New baneshwor shanti binayek tole Madan bhandari, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L56-2</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.331197</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10243,7 +10442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10280,7 +10479,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -10290,7 +10489,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10301,7 +10500,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10512,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 55m</t>
+          <t>3h 48m</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10524,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 9m</t>
+          <t>1d 31m</t>
         </is>
       </c>
     </row>
@@ -10402,10 +10601,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -10592,10 +10791,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -13280,14 +13479,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026 04:24:28 PM</t>
@@ -13311,6 +13510,73 @@
       <c r="M74" s="3" t="inlineStr">
         <is>
           <t>4h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1340092</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Dinesh rai</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:46:23 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:15:01 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW56"/>
+  <dimension ref="A1:AW57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10291,10 +10291,8 @@
           <t>Dinesh rai</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9818733606</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9818733606</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -10329,10 +10327,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.696071</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.696071</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -10384,48 +10380,255 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L56-2</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.331197</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.331197</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2h 28m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 5:20 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340062</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>KTM Ply Trade PVT LTD</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>KTM Ply Trade PVT LTD</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9801894210</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9801894210</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:27:12 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.67779</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Near Motorhead Bikes Nepal, Nayabato Chwok, Dhobighat, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>ktmplytrade@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.30252</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>2h 28m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>2h 52m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10442,7 +10645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10479,7 +10682,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -10489,7 +10692,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -10500,7 +10703,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10715,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 48m</t>
+          <t>3h 42m</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10727,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 31m</t>
+          <t>23h 56m</t>
         </is>
       </c>
     </row>
@@ -10601,10 +10804,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -10791,10 +10994,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -13546,14 +13749,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>20 Sep 2026 05:15:01 PM</t>
@@ -13577,6 +13780,73 @@
       <c r="M75" s="5" t="inlineStr">
         <is>
           <t>2h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340062</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>KTM Ply Trade PVT LTD</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 02:27:12 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 05:20:03 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>2h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_20_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_20_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10490,10 +10490,8 @@
           <t>KTM Ply Trade PVT LTD</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9801894210</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9801894210</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -10528,10 +10526,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.67779</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.67779</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -10587,25 +10583,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.30252</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.30252</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -10654,7 +10646,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13816,7 +13808,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
